--- a/Doc/Sprints.xlsx
+++ b/Doc/Sprints.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kayto\Desktop\IT\Projects\Stage\Stage PFE\Visit_Management\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676AF6F2-85D5-4F8E-8C11-6634399B69A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7CFA47-3896-4157-BD63-659E5849A4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8BBF74DC-B7CA-4A64-921E-927AB595266B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8BBF74DC-B7CA-4A64-921E-927AB595266B}"/>
   </bookViews>
   <sheets>
-    <sheet name="P" sheetId="8" r:id="rId1"/>
-    <sheet name="P1" sheetId="3" r:id="rId2"/>
-    <sheet name="P2" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId1"/>
+    <sheet name="P" sheetId="8" r:id="rId2"/>
+    <sheet name="P1" sheetId="3" r:id="rId3"/>
+    <sheet name="P2" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="457">
   <si>
     <t>📌 Sprint 1: Project Planning &amp; System Design (Week 1-2)</t>
   </si>
@@ -4596,13 +4600,121 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>As a User, I want to securely log in using my credentials so that I can access the platform.</t>
+  </si>
+  <si>
+    <t>As a User, I want to edit my own profile information so that my details are accurate.</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to create new user accounts so that users can access the platform.</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to modify existing user accounts so that user information remains up-to-date.</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to delete user accounts so that inactive or unnecessary accounts can be removed.</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to assign roles to users so that they have appropriate permissions.</t>
+  </si>
+  <si>
+    <t>As an Admin, I want to revoke roles from users so that permissions can be adjusted as needed.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to log visits manually so that I can record visit details when a QR code is unavailable.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to log visits using a QR code scanner so that I can quickly and accurately record visit details.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to validate checklists for each visit so that all required tasks are completed.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to upload photos related to the visit so that visual documentation is available.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to add comments to visit logs so that additional context can be provided.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to view past visit logs so that I can review historical data.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to edit past visit logs so that corrections can be made.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to delete visit logs so that incorrect entries can be removed.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to create new timesheets so that I can manage my weekly schedule.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to update existing timesheets so that changes can be reflected.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to receive real-time notifications for visits so that I know what to do.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to use a responsive mobile application so that I can access the platform conveniently.</t>
+  </si>
+  <si>
+    <t>As a Supervisor, I want to enter data offline so that I can continue working without internet connectivity.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to view and validate timesheets so that accuracy is maintained.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to generate dynamic reports filtered by date range so that specific periods can be analyzed.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to generate dynamic reports filtered by supervisor so that individual performance can be assessed.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to generate dynamic reports filtered by region so that regional performance can be evaluated.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to export reports in PDF format so that they can be shared easily.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to export reports in Excel format so that further analysis can be performed.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to view KPI dashboards with charts and graphs so that key performance indicators can be visualized.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to receive anomaly alerts in dashboards so that issues can be addressed promptly.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to receive real-time notifications for pending validations so that I can take necessary actions.</t>
+  </si>
+  <si>
+    <t>As a Manager, I want to receive real-time notifications for detected anomalies so that timely interventions can occur.</t>
+  </si>
+  <si>
+    <t>As an HR, I want to review timesheets so that employee attendance and performance can be monitored.</t>
+  </si>
+  <si>
+    <t>As an AI Model, I want to analyze timesheet and visit data to detect irregularities so that potential issues can be flagged.</t>
+  </si>
+  <si>
+    <t>As an AI Model, I want to generate automated reports using predictive analytics so that comprehensive insights can be provided.</t>
+  </si>
+  <si>
+    <t>As an AI Model, I want to send real-time alerts based on findings so that relevant users can act immediately.</t>
+  </si>
+  <si>
+    <t>US</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4648,6 +4760,12 @@
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9.6"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -4901,19 +5019,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4990,31 +5102,991 @@
     <xf numFmtId="16" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
-  <dxfs count="61">
+  <dxfs count="60">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5051,977 +6123,6 @@
         <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6037,13 +6138,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{500B39D9-4123-45A0-80A0-E459CD86A349}" name="Table10" displayName="Table10" ref="A4:E36" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{500B39D9-4123-45A0-80A0-E459CD86A349}" name="Table10" displayName="Table10" ref="A4:E36" totalsRowShown="0" headerRowDxfId="59">
   <autoFilter ref="A4:E36" xr:uid="{500B39D9-4123-45A0-80A0-E459CD86A349}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E36">
-    <sortCondition ref="D4:D36"/>
+    <sortCondition descending="1" ref="A4:A36"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{98007FF4-EB8C-4932-863E-DA15154D2479}" name="User Story" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{98007FF4-EB8C-4932-863E-DA15154D2479}" name="User Story" dataDxfId="58"/>
     <tableColumn id="3" xr3:uid="{2726844C-BDDB-43FC-9FF6-4C8C1B91B618}" name="Description"/>
     <tableColumn id="4" xr3:uid="{82C3F325-9E3B-4364-884B-89259BE6652C}" name="BV"/>
     <tableColumn id="5" xr3:uid="{0340ADA4-A753-4492-A1B6-F25D563F3A45}" name="Priority"/>
@@ -6054,109 +6155,109 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{033C4D1A-1A4C-46B3-AE70-00F97870D387}" name="Table2" displayName="Table2" ref="B32:D43" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{033C4D1A-1A4C-46B3-AE70-00F97870D387}" name="Table2" displayName="Table2" ref="B32:D43" totalsRowShown="0" headerRowDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3" headerRowCellStyle="Output">
   <autoFilter ref="B32:D43" xr:uid="{033C4D1A-1A4C-46B3-AE70-00F97870D387}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{54132C3A-94B6-4877-8002-96299AE182E3}" name="Day" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{3A768890-429B-4AFB-86E7-80708B149B57}" name="Tasks" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{DB982DC2-6C15-4D43-800E-6FE5A1192B56}" name="Deliverables" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{54132C3A-94B6-4877-8002-96299AE182E3}" name="Day" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3A768890-429B-4AFB-86E7-80708B149B57}" name="Tasks" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{DB982DC2-6C15-4D43-800E-6FE5A1192B56}" name="Deliverables" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5591589C-AF51-4683-9559-8C08947930D6}" name="Table9" displayName="Table9" ref="A1:D49" headerRowDxfId="17" tableBorderDxfId="16" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{5591589C-AF51-4683-9559-8C08947930D6}" name="Table9" displayName="Table9" ref="A1:D49" headerRowDxfId="57" tableBorderDxfId="56" headerRowCellStyle="Output">
   <autoFilter ref="A1:D49" xr:uid="{5591589C-AF51-4683-9559-8C08947930D6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D4FB61AC-AD01-48AB-908E-22D58E29B9EA}" name="Week" totalsRowLabel="Total" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{5013AD8C-D89F-4F5D-995F-CCDCE83C1D70}" name="Phase" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{FF432DAF-CA0F-4054-8FD9-3942E57453AD}" name="Detailed Tasks" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{AF26860E-3DF1-46CA-B156-5EA1C16C49DA}" name="Deliverables" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{D4FB61AC-AD01-48AB-908E-22D58E29B9EA}" name="Week" totalsRowLabel="Total" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{5013AD8C-D89F-4F5D-995F-CCDCE83C1D70}" name="Phase" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{FF432DAF-CA0F-4054-8FD9-3942E57453AD}" name="Detailed Tasks" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{AF26860E-3DF1-46CA-B156-5EA1C16C49DA}" name="Deliverables" totalsRowFunction="count" dataDxfId="49" totalsRowDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17066829-33E1-447F-9593-5E62D6AD4042}" name="Table1" displayName="Table1" ref="B6:D25" totalsRowShown="0" headerRowDxfId="55" tableBorderDxfId="60" totalsRowBorderDxfId="59" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{17066829-33E1-447F-9593-5E62D6AD4042}" name="Table1" displayName="Table1" ref="B6:D25" totalsRowShown="0" headerRowDxfId="47" tableBorderDxfId="46" totalsRowBorderDxfId="45" headerRowCellStyle="Output">
   <autoFilter ref="B6:D25" xr:uid="{17066829-33E1-447F-9593-5E62D6AD4042}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{55B9F087-4C8D-4DCF-85AD-0A8C238D71FD}" name="Day" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{9E712EBB-02E3-4279-9C5E-D79930D485C6}" name="Tasks" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{646143AE-CB6B-412D-B2B4-87420482777E}" name="Deliverables" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{55B9F087-4C8D-4DCF-85AD-0A8C238D71FD}" name="Day" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{9E712EBB-02E3-4279-9C5E-D79930D485C6}" name="Tasks" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{646143AE-CB6B-412D-B2B4-87420482777E}" name="Deliverables" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D91BA07A-185E-469B-A981-66CEF1FDD526}" name="Table3" displayName="Table3" ref="B50:D59" totalsRowShown="0" headerRowDxfId="48" tableBorderDxfId="53" totalsRowBorderDxfId="52" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D91BA07A-185E-469B-A981-66CEF1FDD526}" name="Table3" displayName="Table3" ref="B50:D59" totalsRowShown="0" headerRowDxfId="41" tableBorderDxfId="40" totalsRowBorderDxfId="39" headerRowCellStyle="Output">
   <autoFilter ref="B50:D59" xr:uid="{D91BA07A-185E-469B-A981-66CEF1FDD526}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{98811E1C-DD53-4D3C-BCFA-CF625791BF62}" name="Day" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{E79A0293-5D27-4EFD-809D-34E1DAFB3525}" name="Tasks" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{972007B0-3B96-40D0-AB2D-6D76CD270BED}" name="Deliverables" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{98811E1C-DD53-4D3C-BCFA-CF625791BF62}" name="Day" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{E79A0293-5D27-4EFD-809D-34E1DAFB3525}" name="Tasks" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{972007B0-3B96-40D0-AB2D-6D76CD270BED}" name="Deliverables" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CBD74806-1199-4347-B0EC-B1D120068AB1}" name="Table4" displayName="Table4" ref="B66:D71" totalsRowShown="0" headerRowDxfId="42" tableBorderDxfId="47" totalsRowBorderDxfId="46" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CBD74806-1199-4347-B0EC-B1D120068AB1}" name="Table4" displayName="Table4" ref="B66:D71" totalsRowShown="0" headerRowDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33" headerRowCellStyle="Output">
   <autoFilter ref="B66:D71" xr:uid="{CBD74806-1199-4347-B0EC-B1D120068AB1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DD5A17FA-48F4-4608-AF17-D193C392EE0E}" name="Day" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{D4C6025F-C8E4-4D7C-BDEC-123301C31A20}" name="Tasks" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{9D2209A4-6189-4C83-8B70-B78A9D9AF03C}" name="Deliverables" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{DD5A17FA-48F4-4608-AF17-D193C392EE0E}" name="Day" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{D4C6025F-C8E4-4D7C-BDEC-123301C31A20}" name="Tasks" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{9D2209A4-6189-4C83-8B70-B78A9D9AF03C}" name="Deliverables" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0299898-7628-4DAF-BABC-4778D900D5F1}" name="Table5" displayName="Table5" ref="B78:D90" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="41" totalsRowBorderDxfId="40" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0299898-7628-4DAF-BABC-4778D900D5F1}" name="Table5" displayName="Table5" ref="B78:D90" totalsRowShown="0" headerRowDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27" headerRowCellStyle="Output">
   <autoFilter ref="B78:D90" xr:uid="{D0299898-7628-4DAF-BABC-4778D900D5F1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F22CFAA3-69D6-4AEC-AC23-B4B67883E6B7}" name="Day" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{02118265-D45A-4385-AF44-645E94AE1883}" name="Tasks" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{1057EDBA-ABDD-45E8-A658-7FE3BC04EC22}" name="Deliverables" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{F22CFAA3-69D6-4AEC-AC23-B4B67883E6B7}" name="Day" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{02118265-D45A-4385-AF44-645E94AE1883}" name="Tasks" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{1057EDBA-ABDD-45E8-A658-7FE3BC04EC22}" name="Deliverables" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{58B34FF1-CC8E-492B-B362-EE11FF7B568E}" name="Table6" displayName="Table6" ref="B97:D108" totalsRowShown="0" headerRowDxfId="30" tableBorderDxfId="35" totalsRowBorderDxfId="34" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{58B34FF1-CC8E-492B-B362-EE11FF7B568E}" name="Table6" displayName="Table6" ref="B97:D108" totalsRowShown="0" headerRowDxfId="23" tableBorderDxfId="22" totalsRowBorderDxfId="21" headerRowCellStyle="Output">
   <autoFilter ref="B97:D108" xr:uid="{58B34FF1-CC8E-492B-B362-EE11FF7B568E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{23208640-9F2D-4326-8B5B-7FBEBDF98826}" name="Day" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{3FBE890D-5427-454F-8ABB-566E2D9AFA3A}" name="Tasks" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{1B956508-AB3E-402A-8073-5DE4261BAE5D}" name="Deliverables" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{23208640-9F2D-4326-8B5B-7FBEBDF98826}" name="Day" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{3FBE890D-5427-454F-8ABB-566E2D9AFA3A}" name="Tasks" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{1B956508-AB3E-402A-8073-5DE4261BAE5D}" name="Deliverables" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{30B4ECEA-D99C-4049-BC61-D2A4EE2457AC}" name="Table7" displayName="Table7" ref="B115:D126" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="29" totalsRowBorderDxfId="28" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{30B4ECEA-D99C-4049-BC61-D2A4EE2457AC}" name="Table7" displayName="Table7" ref="B115:D126" totalsRowShown="0" headerRowDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15" headerRowCellStyle="Output">
   <autoFilter ref="B115:D126" xr:uid="{30B4ECEA-D99C-4049-BC61-D2A4EE2457AC}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{59E6FB9C-6DD4-41B2-91F4-846693C26806}" name="Day" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{E3B71C4F-9559-40ED-AA15-CCF9FC15E8D7}" name="Tasks" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{9D9573C9-7ED6-4148-A7A0-F3592C86E7AC}" name="Deliverables" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{59E6FB9C-6DD4-41B2-91F4-846693C26806}" name="Day" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{E3B71C4F-9559-40ED-AA15-CCF9FC15E8D7}" name="Tasks" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{9D9573C9-7ED6-4148-A7A0-F3592C86E7AC}" name="Deliverables" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A74DBDD1-754D-442E-9F7E-16933CBFD0C7}" name="Table8" displayName="Table8" ref="B133:D144" totalsRowShown="0" headerRowDxfId="18" tableBorderDxfId="23" totalsRowBorderDxfId="22" headerRowCellStyle="Output">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A74DBDD1-754D-442E-9F7E-16933CBFD0C7}" name="Table8" displayName="Table8" ref="B133:D144" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9" headerRowCellStyle="Output">
   <autoFilter ref="B133:D144" xr:uid="{A74DBDD1-754D-442E-9F7E-16933CBFD0C7}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7F3A765B-7316-48C9-BB54-E30374B3CF27}" name="Day" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{6E14C0FD-F615-4073-B1C2-3F96414DEE26}" name="Tasks" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{FC58AE58-E097-4AB1-8989-226E461B6366}" name="Deliverables" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{7F3A765B-7316-48C9-BB54-E30374B3CF27}" name="Day" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{6E14C0FD-F615-4073-B1C2-3F96414DEE26}" name="Tasks" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{FC58AE58-E097-4AB1-8989-226E461B6366}" name="Deliverables" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="1"/>
 </table>
@@ -6478,6 +6579,620 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E82697-5109-4A0A-8FB1-F66196353EB7}">
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="113.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="33">
+        <v>8</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D2" s="33">
+        <v>1</v>
+      </c>
+      <c r="E2" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="33">
+        <v>9</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D3" s="33">
+        <v>2</v>
+      </c>
+      <c r="E3" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="33">
+        <v>10</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D4" s="33">
+        <v>3</v>
+      </c>
+      <c r="E4" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="33">
+        <v>16</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D5" s="33">
+        <v>4</v>
+      </c>
+      <c r="E5" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="33">
+        <v>21</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" s="33">
+        <v>5</v>
+      </c>
+      <c r="E6" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="33">
+        <v>22</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D7" s="33">
+        <v>6</v>
+      </c>
+      <c r="E7" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="33">
+        <v>27</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="33">
+        <v>7</v>
+      </c>
+      <c r="E8" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="33">
+        <v>32</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="33">
+        <v>8</v>
+      </c>
+      <c r="E9" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
+        <v>1</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="33">
+        <v>9</v>
+      </c>
+      <c r="E10" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="33">
+        <v>3</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="33">
+        <v>10</v>
+      </c>
+      <c r="E11" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="33">
+        <v>6</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D12" s="33">
+        <v>11</v>
+      </c>
+      <c r="E12" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="33">
+        <v>18</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="33">
+        <v>12</v>
+      </c>
+      <c r="E13" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="33">
+        <v>19</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D14" s="33">
+        <v>13</v>
+      </c>
+      <c r="E14" s="33">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="33">
+        <v>20</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="33">
+        <v>14</v>
+      </c>
+      <c r="E15" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="33">
+        <v>23</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D16" s="33">
+        <v>15</v>
+      </c>
+      <c r="E16" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="33">
+        <v>24</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D17" s="33">
+        <v>16</v>
+      </c>
+      <c r="E17" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="33">
+        <v>25</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D18" s="33">
+        <v>17</v>
+      </c>
+      <c r="E18" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="33">
+        <v>26</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D19" s="33">
+        <v>18</v>
+      </c>
+      <c r="E19" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="33">
+        <v>28</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D20" s="33">
+        <v>19</v>
+      </c>
+      <c r="E20" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="33">
+        <v>29</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="33">
+        <v>20</v>
+      </c>
+      <c r="E21" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="33">
+        <v>30</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="33">
+        <v>21</v>
+      </c>
+      <c r="E22" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="33">
+        <v>33</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D23" s="33">
+        <v>22</v>
+      </c>
+      <c r="E23" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="33">
+        <v>34</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D24" s="33">
+        <v>23</v>
+      </c>
+      <c r="E24" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="33">
+        <v>2</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D25" s="33">
+        <v>24</v>
+      </c>
+      <c r="E25" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="33">
+        <v>4</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D26" s="33">
+        <v>25</v>
+      </c>
+      <c r="E26" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="33">
+        <v>5</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="33">
+        <v>26</v>
+      </c>
+      <c r="E27" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="33">
+        <v>7</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>428</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D28" s="33">
+        <v>27</v>
+      </c>
+      <c r="E28" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="33">
+        <v>11</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D29" s="33">
+        <v>28</v>
+      </c>
+      <c r="E29" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="33">
+        <v>12</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D30" s="33">
+        <v>29</v>
+      </c>
+      <c r="E30" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="33">
+        <v>13</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D31" s="33">
+        <v>30</v>
+      </c>
+      <c r="E31" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="33">
+        <v>14</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D32" s="33">
+        <v>31</v>
+      </c>
+      <c r="E32" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="33">
+        <v>15</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D33" s="33">
+        <v>32</v>
+      </c>
+      <c r="E33" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="33">
+        <v>17</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>438</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D34" s="33">
+        <v>33</v>
+      </c>
+      <c r="E34" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="33">
+        <v>31</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>355</v>
+      </c>
+      <c r="D35" s="33">
+        <v>34</v>
+      </c>
+      <c r="E35" s="33">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E35" xr:uid="{28E82697-5109-4A0A-8FB1-F66196353EB7}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734E54BD-771A-427B-8F95-53F089C3CC40}">
   <dimension ref="A4:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6488,575 +7203,576 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="30" t="s">
         <v>349</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="30" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
-        <v>358</v>
+      <c r="A5" t="s">
+        <v>418</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="C5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
-        <v>360</v>
+      <c r="A6" t="s">
+        <v>406</v>
       </c>
       <c r="B6" t="s">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
-        <v>380</v>
+      <c r="A7" t="s">
+        <v>388</v>
       </c>
       <c r="B7" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
         <v>354</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
-        <v>362</v>
+      <c r="A8" t="s">
+        <v>404</v>
       </c>
       <c r="B8" t="s">
-        <v>363</v>
+        <v>405</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
-        <v>364</v>
+      <c r="A9" t="s">
+        <v>396</v>
       </c>
       <c r="B9" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
-        <v>370</v>
+      <c r="A10" t="s">
+        <v>398</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
-        <v>369</v>
+      <c r="A11" t="s">
+        <v>356</v>
       </c>
       <c r="B11" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="C11" t="s">
         <v>353</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C12" t="s">
+        <v>354</v>
+      </c>
+      <c r="D12">
+        <v>22</v>
+      </c>
+      <c r="E12">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="B12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C12" t="s">
-        <v>353</v>
-      </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>13</v>
-      </c>
-    </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
-        <v>376</v>
+      <c r="A13" t="s">
+        <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>378</v>
+      <c r="A14" t="s">
+        <v>400</v>
       </c>
       <c r="B14" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C14" t="s">
         <v>354</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>382</v>
+      <c r="A15" t="s">
+        <v>414</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
         <v>354</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E15">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
-        <v>384</v>
+      <c r="A16" t="s">
+        <v>412</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
         <v>354</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
-        <v>386</v>
+      <c r="A17" t="s">
+        <v>384</v>
       </c>
       <c r="B17" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C17" t="s">
         <v>354</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
-        <v>374</v>
+      <c r="A18" t="s">
+        <v>360</v>
       </c>
       <c r="B18" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="C18" t="s">
         <v>353</v>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
-        <v>356</v>
+      <c r="A19" t="s">
+        <v>380</v>
       </c>
       <c r="B19" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E19">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>390</v>
+      <c r="A20" t="s">
+        <v>382</v>
       </c>
       <c r="B20" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C20" t="s">
         <v>354</v>
       </c>
       <c r="D20">
+        <v>11</v>
+      </c>
+      <c r="E20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>358</v>
+      </c>
+      <c r="B21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>410</v>
+      </c>
+      <c r="B22" t="s">
+        <v>411</v>
+      </c>
+      <c r="C22" t="s">
+        <v>355</v>
+      </c>
+      <c r="D22">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" t="s">
+        <v>363</v>
+      </c>
+      <c r="C23" t="s">
+        <v>353</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>390</v>
+      </c>
+      <c r="B24" t="s">
+        <v>391</v>
+      </c>
+      <c r="C24" t="s">
+        <v>354</v>
+      </c>
+      <c r="D24">
         <v>16</v>
       </c>
-      <c r="E20">
+      <c r="E24">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
-        <v>388</v>
-      </c>
-      <c r="B21" t="s">
-        <v>389</v>
-      </c>
-      <c r="C21" t="s">
-        <v>354</v>
-      </c>
-      <c r="D21">
-        <v>17</v>
-      </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>406</v>
-      </c>
-      <c r="B22" t="s">
-        <v>407</v>
-      </c>
-      <c r="C22" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22">
-        <v>18</v>
-      </c>
-      <c r="E22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="B23" t="s">
-        <v>403</v>
-      </c>
-      <c r="C23" t="s">
-        <v>354</v>
-      </c>
-      <c r="D23">
-        <v>19</v>
-      </c>
-      <c r="E23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
-        <v>372</v>
-      </c>
-      <c r="B24" t="s">
-        <v>373</v>
-      </c>
-      <c r="C24" t="s">
-        <v>353</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
-      </c>
-      <c r="E24">
-        <v>13</v>
-      </c>
-    </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
-        <v>392</v>
+      <c r="A25" t="s">
+        <v>378</v>
       </c>
       <c r="B25" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="C25" t="s">
         <v>354</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="35" t="s">
-        <v>394</v>
+      <c r="A26" t="s">
+        <v>376</v>
       </c>
       <c r="B26" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C26" t="s">
         <v>354</v>
       </c>
       <c r="D26">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E26">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" t="s">
+        <v>371</v>
+      </c>
+      <c r="C27" t="s">
+        <v>353</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
-        <v>404</v>
-      </c>
-      <c r="B27" t="s">
-        <v>405</v>
-      </c>
-      <c r="C27" t="s">
-        <v>354</v>
-      </c>
-      <c r="D27">
-        <v>23</v>
-      </c>
-      <c r="E27">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>364</v>
+      </c>
+      <c r="B28" t="s">
+        <v>365</v>
+      </c>
+      <c r="C28" t="s">
+        <v>353</v>
+      </c>
+      <c r="D28">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
-        <v>396</v>
-      </c>
-      <c r="B28" t="s">
-        <v>397</v>
-      </c>
-      <c r="C28" t="s">
-        <v>354</v>
-      </c>
-      <c r="D28">
-        <v>24</v>
-      </c>
       <c r="E28">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
-        <v>398</v>
+      <c r="A29" t="s">
+        <v>402</v>
       </c>
       <c r="B29" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C29" t="s">
         <v>354</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="35" t="s">
-        <v>412</v>
+      <c r="A30" t="s">
+        <v>416</v>
       </c>
       <c r="B30" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C30" t="s">
+        <v>354</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>366</v>
+      </c>
+      <c r="B31" t="s">
+        <v>367</v>
+      </c>
+      <c r="C31" t="s">
         <v>353</v>
       </c>
-      <c r="D30">
-        <v>26</v>
-      </c>
-      <c r="E30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>400</v>
-      </c>
-      <c r="B31" t="s">
-        <v>401</v>
-      </c>
-      <c r="C31" t="s">
-        <v>354</v>
-      </c>
       <c r="D31">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
-        <v>414</v>
+      <c r="A32" t="s">
+        <v>369</v>
       </c>
       <c r="B32" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="C32" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D32">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E32">
         <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>418</v>
+      <c r="A33" t="s">
+        <v>386</v>
       </c>
       <c r="B33" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="C33" t="s">
         <v>354</v>
       </c>
       <c r="D33">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
-        <v>416</v>
+      <c r="A34" t="s">
+        <v>392</v>
       </c>
       <c r="B34" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="C34" t="s">
         <v>354</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
-        <v>410</v>
+      <c r="A35" t="s">
+        <v>374</v>
       </c>
       <c r="B35" t="s">
-        <v>411</v>
+        <v>375</v>
       </c>
       <c r="C35" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D35">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="35" t="s">
-        <v>408</v>
+      <c r="A36" t="s">
+        <v>372</v>
       </c>
       <c r="B36" t="s">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="C36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D36">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB920591-DE19-497C-A3FA-8292D8F525BA}">
   <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7068,494 +7784,494 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="22" t="s">
         <v>261</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="13" t="s">
+      <c r="A3" s="18"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="18"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="15" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
+      <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="13" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="13" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="13" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="D9" s="17"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
+      <c r="A11" s="13">
         <v>3</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="13" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="13" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="D13" s="17"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="18"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="D14" s="17"/>
+      <c r="D14" s="15"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="11" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="D15" s="18"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>4</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="13" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="15" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="13" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="D18" s="17"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="13" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="D19" s="17"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="14" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="D20" s="19"/>
+      <c r="D20" s="17"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="15">
+      <c r="A21" s="13">
         <v>5</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="18"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="15" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="13" t="s">
+      <c r="A23" s="18"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D23" s="17"/>
+      <c r="D23" s="15"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="11" t="s">
+      <c r="A24" s="5"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="16"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
+      <c r="A25" s="19">
         <v>6</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="20"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="13" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="20"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="13" t="s">
+      <c r="A27" s="18"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="D27" s="17"/>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D28" s="19"/>
+      <c r="D28" s="17"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
+      <c r="A29" s="13">
         <v>7</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="14" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="13" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="15" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="13" t="s">
+      <c r="A31" s="18"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="D31" s="17"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="13" t="s">
+      <c r="A32" s="5"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="D32" s="17"/>
+      <c r="D32" s="15"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="21">
+      <c r="A33" s="19">
         <v>8</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="13" t="s">
+      <c r="A34" s="18"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D34" s="17"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="D35" s="19"/>
+      <c r="D35" s="17"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="23" t="s">
         <v>268</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="14" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="13" t="s">
+      <c r="A37" s="18"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="15" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="30"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="13" t="s">
+      <c r="A38" s="18"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="D38" s="17"/>
+      <c r="D38" s="15"/>
     </row>
     <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="31"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="25"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="D39" s="19"/>
+      <c r="D39" s="17"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="28" t="s">
         <v>348</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="14" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="13" t="s">
+      <c r="A41" s="18"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="D41" s="17"/>
+      <c r="D41" s="15"/>
     </row>
     <row r="42" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="31"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="25"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="D42" s="19"/>
+      <c r="D42" s="17"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="14" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="20"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="13" t="s">
+      <c r="A44" s="18"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="D44" s="17"/>
+      <c r="D44" s="15"/>
     </row>
     <row r="45" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="14" t="s">
+      <c r="A45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="12" t="s">
         <v>340</v>
       </c>
-      <c r="D45" s="19"/>
+      <c r="D45" s="17"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="13" t="s">
+      <c r="A47" s="18"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D47" s="17"/>
+      <c r="D47" s="15"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="13" t="s">
+      <c r="A48" s="18"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="D48" s="17"/>
+      <c r="D48" s="15"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="13" t="s">
+      <c r="A49" s="18"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D49" s="17"/>
+      <c r="D49" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7565,7 +8281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E2F158-B630-43FD-B100-456BC9C5131A}">
   <dimension ref="B2:D144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7578,1143 +8294,1143 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="16"/>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="29"/>
+      <c r="C10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="33"/>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="29"/>
+      <c r="C12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="18"/>
+      <c r="D12" s="16"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="33"/>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="29"/>
+      <c r="C14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="33"/>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="29"/>
+      <c r="C16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="18"/>
+      <c r="D16" s="16"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="33"/>
-      <c r="C19" s="11" t="s">
+      <c r="B19" s="29"/>
+      <c r="C19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="16"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="33"/>
-      <c r="C21" s="11" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="18"/>
+      <c r="D21" s="16"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="33"/>
-      <c r="C23" s="11" t="s">
+      <c r="B23" s="29"/>
+      <c r="C23" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="18"/>
+      <c r="D23" s="16"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="33"/>
-      <c r="C34" s="11" t="s">
+      <c r="B34" s="29"/>
+      <c r="C34" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="D34" s="16"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="4" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="24" t="s">
+      <c r="D50" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="4" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="4" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="8" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="62" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D66" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="4" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="4" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="8" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="74" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="8" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B80" s="33"/>
-      <c r="C80" s="11" t="s">
+      <c r="B80" s="29"/>
+      <c r="C80" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="D80" s="18"/>
+      <c r="D80" s="16"/>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="D81" s="4" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="4" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="4" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="93" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="35"/>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B97" s="24" t="s">
+      <c r="B97" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C97" s="24" t="s">
+      <c r="C97" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="4" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="4" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="4" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="8" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="111" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="C111" s="34"/>
+      <c r="D111" s="34"/>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
+      <c r="C113" s="35"/>
+      <c r="D113" s="35"/>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C115" s="24" t="s">
+      <c r="C115" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D115" s="24" t="s">
+      <c r="D115" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="4" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B117" s="5" t="s">
+      <c r="B117" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="D117" s="4" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="4" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="D120" s="4" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="D121" s="4" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="4" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D123" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="D124" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="D125" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="8" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="129" spans="2:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="C129" s="34"/>
+      <c r="D129" s="34"/>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="C131" s="4"/>
-      <c r="D131" s="4"/>
+      <c r="C131" s="35"/>
+      <c r="D131" s="35"/>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C133" s="24" t="s">
+      <c r="C133" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D133" s="24" t="s">
+      <c r="D133" s="22" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B134" s="5" t="s">
+      <c r="B134" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="4" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B135" s="5" t="s">
+      <c r="B135" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="D135" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B136" s="5" t="s">
+      <c r="B136" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D136" s="6" t="s">
+      <c r="D136" s="4" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="4" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B139" s="5" t="s">
+      <c r="B139" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="D139" s="4" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="4" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="141" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="D141" s="4" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="4" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="4" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="8" t="s">
         <v>259</v>
       </c>
     </row>
@@ -8730,12 +9446,12 @@
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="B95:D95"/>
     <mergeCell ref="B113:D113"/>
+    <mergeCell ref="B93:D93"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B93:D93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
